--- a/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_6AM.xlsx
+++ b/NuevasNotas/Matutina/Resultados_Auditoria_Notas/Matriz_Marcada_6AM.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Matriz Final Sexto A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RESUMEN DISCREPANCIAS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Matriz Final Sexto A" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +51,24 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -60,6 +77,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A8A"/>
+        <bgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B82F6"/>
+        <bgColor rgb="003B82F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D1FAE5"/>
+        <bgColor rgb="00D1FAE5"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -132,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -167,6 +202,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,6 +576,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>RESUMEN DE AUDITORÍA (DISCREPANCIAS ENCONTRADAS)</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="n"/>
+      <c r="C1" s="14" t="n"/>
+      <c r="D1" s="14" t="n"/>
+      <c r="E1" s="14" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>▶ CURSO: 6AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="25" customHeight="1">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>✅ Todo el curso está perfectamente cuadrado. No hay discrepancias.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -573,7 +668,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
